--- a/results/eval/SUMMARY-mtbench-alpaca.xlsx
+++ b/results/eval/SUMMARY-mtbench-alpaca.xlsx
@@ -1,16 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Paper Table" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MT-Bench Detail" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AlpacaEval Detail" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Distillation Gap" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Paper Table" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="MT-Bench Detail" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="AlpacaEval Detail" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Distillation Gap" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Pairwise Qwen" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Pairwise Llama" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Pairwise Details" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,8 +22,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="4">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.000"/>
+  </numFmts>
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -39,8 +44,15 @@
     <font>
       <i val="1"/>
     </font>
+    <font>
+      <i val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -71,6 +83,24 @@
         <bgColor rgb="00F8CBAD"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
+        <bgColor rgb="00FFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
+        <bgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -98,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -129,6 +159,21 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -515,7 +560,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -935,7 +979,6 @@
         <v>805</v>
       </c>
     </row>
-    <row r="16"/>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
@@ -943,7 +986,6 @@
         </is>
       </c>
     </row>
-    <row r="18"/>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
@@ -3673,7 +3715,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
@@ -3908,8 +3949,6 @@
         </is>
       </c>
     </row>
-    <row r="16"/>
-    <row r="17"/>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
@@ -3938,7 +3977,6 @@
         </is>
       </c>
     </row>
-    <row r="22"/>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
@@ -4203,4 +4241,1648 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Pairwise MT-Bench - Qwen 1.7B Ours vs baselines</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="12" t="inlineStr">
+        <is>
+          <t>Each cell = WR = (wins + 0.5*ties) / total over 80Q x 2 turns x 2 swaps. Judge: gpt-5.4-mini.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="12" t="inlineStr">
+        <is>
+          <t>GREEN = Ours WIN (WR&gt;0.55) | YELLOW = TIE | RED = Baseline win (WR&lt;0.45)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4"/>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Anchor (Ours)</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>vs dpo</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>vs wpo</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>vs radpo</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>vs dckd</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>vs adpa</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>vs tvkd</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>tailriskKD</t>
+        </is>
+      </c>
+      <c r="B6" s="14" t="n">
+        <v>0.5062</v>
+      </c>
+      <c r="C6" s="14" t="n">
+        <v>0.5189</v>
+      </c>
+      <c r="D6" s="15" t="n">
+        <v>0.6844</v>
+      </c>
+      <c r="E6" s="14" t="n">
+        <v>0.4562</v>
+      </c>
+      <c r="F6" s="15" t="n">
+        <v>0.8781</v>
+      </c>
+      <c r="G6" s="15" t="n">
+        <v>0.6125</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>pfw-tail</t>
+        </is>
+      </c>
+      <c r="B7" s="14" t="n">
+        <v>0.5219</v>
+      </c>
+      <c r="C7" s="14" t="n">
+        <v>0.5344</v>
+      </c>
+      <c r="D7" s="15" t="n">
+        <v>0.6719000000000001</v>
+      </c>
+      <c r="E7" s="16" t="n">
+        <v>0.4031</v>
+      </c>
+      <c r="F7" s="15" t="n">
+        <v>0.8781</v>
+      </c>
+      <c r="G7" s="15" t="n">
+        <v>0.6094000000000001</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>riskKD</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="n">
+        <v>0.481</v>
+      </c>
+      <c r="C8" s="14" t="n">
+        <v>0.5125</v>
+      </c>
+      <c r="D8" s="15" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="E8" s="16" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F8" s="15" t="n">
+        <v>0.8875</v>
+      </c>
+      <c r="G8" s="15" t="n">
+        <v>0.6281</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Pairwise MT-Bench - Llama 3.2-1B Ours vs baselines</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="12" t="inlineStr">
+        <is>
+          <t>Each cell = WR = (wins + 0.5*ties) / total over 80Q x 2 turns x 2 swaps. Judge: gpt-5.4-mini.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="12" t="inlineStr">
+        <is>
+          <t>GREEN = Ours WIN (WR&gt;0.55) | YELLOW = TIE | RED = Baseline win (WR&lt;0.45)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4"/>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Anchor (Ours)</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>vs dckd</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>vs adpa</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>vs tvkd</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>tailriskKD</t>
+        </is>
+      </c>
+      <c r="B6" s="16" t="n">
+        <v>0.2875</v>
+      </c>
+      <c r="C6" s="15" t="n">
+        <v>0.925</v>
+      </c>
+      <c r="D6" s="14" t="n">
+        <v>0.4874</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>pfw-tail</t>
+        </is>
+      </c>
+      <c r="B7" s="16" t="n">
+        <v>0.2406</v>
+      </c>
+      <c r="C7" s="15" t="n">
+        <v>0.9156</v>
+      </c>
+      <c r="D7" s="14" t="n">
+        <v>0.4594</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>riskkd (tokenwt)</t>
+        </is>
+      </c>
+      <c r="B8" s="16" t="n">
+        <v>0.07190000000000001</v>
+      </c>
+      <c r="C8" s="15" t="n">
+        <v>0.6656</v>
+      </c>
+      <c r="D8" s="16" t="n">
+        <v>0.08749999999999999</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="7" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Family</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Anchor (Ours)</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Baseline</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Wins</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Losses</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>Ties</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>Errors</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>n_total</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>Win Rate</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>WR Turn 1</t>
+        </is>
+      </c>
+      <c r="K1" s="2" t="inlineStr">
+        <is>
+          <t>WR Turn 2</t>
+        </is>
+      </c>
+      <c r="L1" s="2" t="inlineStr">
+        <is>
+          <t>Tokens In</t>
+        </is>
+      </c>
+      <c r="M1" s="2" t="inlineStr">
+        <is>
+          <t>Tokens Out</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="17" t="inlineStr">
+        <is>
+          <t>qwen3-1.7b</t>
+        </is>
+      </c>
+      <c r="B2" s="17" t="inlineStr">
+        <is>
+          <t>tailriskKD</t>
+        </is>
+      </c>
+      <c r="C2" s="17" t="inlineStr">
+        <is>
+          <t>dpo</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="n">
+        <v>46</v>
+      </c>
+      <c r="E2" s="6" t="n">
+        <v>44</v>
+      </c>
+      <c r="F2" s="6" t="n">
+        <v>70</v>
+      </c>
+      <c r="G2" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" s="6" t="n">
+        <v>160</v>
+      </c>
+      <c r="I2" s="14" t="n">
+        <v>0.5062</v>
+      </c>
+      <c r="J2" s="18" t="n">
+        <v>0.4938</v>
+      </c>
+      <c r="K2" s="18" t="n">
+        <v>0.5188</v>
+      </c>
+      <c r="L2" s="6" t="n">
+        <v>983072</v>
+      </c>
+      <c r="M2" s="6" t="n">
+        <v>16045</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="17" t="inlineStr">
+        <is>
+          <t>qwen3-1.7b</t>
+        </is>
+      </c>
+      <c r="B3" s="17" t="inlineStr">
+        <is>
+          <t>tailriskKD</t>
+        </is>
+      </c>
+      <c r="C3" s="17" t="inlineStr">
+        <is>
+          <t>wpo</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="n">
+        <v>51</v>
+      </c>
+      <c r="E3" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="F3" s="6" t="n">
+        <v>63</v>
+      </c>
+      <c r="G3" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" s="6" t="n">
+        <v>159</v>
+      </c>
+      <c r="I3" s="14" t="n">
+        <v>0.5189</v>
+      </c>
+      <c r="J3" s="18" t="n">
+        <v>0.4625</v>
+      </c>
+      <c r="K3" s="18" t="n">
+        <v>0.5759</v>
+      </c>
+      <c r="L3" s="6" t="n">
+        <v>1004758</v>
+      </c>
+      <c r="M3" s="6" t="n">
+        <v>15083</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="17" t="inlineStr">
+        <is>
+          <t>qwen3-1.7b</t>
+        </is>
+      </c>
+      <c r="B4" s="17" t="inlineStr">
+        <is>
+          <t>tailriskKD</t>
+        </is>
+      </c>
+      <c r="C4" s="17" t="inlineStr">
+        <is>
+          <t>radpo</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>80</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>21</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>59</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>160</v>
+      </c>
+      <c r="I4" s="15" t="n">
+        <v>0.6844</v>
+      </c>
+      <c r="J4" s="18" t="n">
+        <v>0.6875</v>
+      </c>
+      <c r="K4" s="18" t="n">
+        <v>0.6813</v>
+      </c>
+      <c r="L4" s="6" t="n">
+        <v>1005342</v>
+      </c>
+      <c r="M4" s="6" t="n">
+        <v>16246</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="17" t="inlineStr">
+        <is>
+          <t>qwen3-1.7b</t>
+        </is>
+      </c>
+      <c r="B5" s="17" t="inlineStr">
+        <is>
+          <t>tailriskKD</t>
+        </is>
+      </c>
+      <c r="C5" s="17" t="inlineStr">
+        <is>
+          <t>dckd</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>39</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>53</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>68</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>160</v>
+      </c>
+      <c r="I5" s="14" t="n">
+        <v>0.4562</v>
+      </c>
+      <c r="J5" s="18" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="K5" s="18" t="n">
+        <v>0.4625</v>
+      </c>
+      <c r="L5" s="6" t="n">
+        <v>720640</v>
+      </c>
+      <c r="M5" s="6" t="n">
+        <v>22508</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="17" t="inlineStr">
+        <is>
+          <t>qwen3-1.7b</t>
+        </is>
+      </c>
+      <c r="B6" s="17" t="inlineStr">
+        <is>
+          <t>tailriskKD</t>
+        </is>
+      </c>
+      <c r="C6" s="17" t="inlineStr">
+        <is>
+          <t>adpa</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>125</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>31</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>160</v>
+      </c>
+      <c r="I6" s="15" t="n">
+        <v>0.8781</v>
+      </c>
+      <c r="J6" s="18" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="K6" s="18" t="n">
+        <v>0.8562</v>
+      </c>
+      <c r="L6" s="6" t="n">
+        <v>886340</v>
+      </c>
+      <c r="M6" s="6" t="n">
+        <v>20455</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="17" t="inlineStr">
+        <is>
+          <t>qwen3-1.7b</t>
+        </is>
+      </c>
+      <c r="B7" s="17" t="inlineStr">
+        <is>
+          <t>tailriskKD</t>
+        </is>
+      </c>
+      <c r="C7" s="17" t="inlineStr">
+        <is>
+          <t>tvkd</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>72</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>36</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>52</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>160</v>
+      </c>
+      <c r="I7" s="15" t="n">
+        <v>0.6125</v>
+      </c>
+      <c r="J7" s="18" t="n">
+        <v>0.6062</v>
+      </c>
+      <c r="K7" s="18" t="n">
+        <v>0.6188</v>
+      </c>
+      <c r="L7" s="6" t="n">
+        <v>1001686</v>
+      </c>
+      <c r="M7" s="6" t="n">
+        <v>17335</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="17" t="inlineStr">
+        <is>
+          <t>qwen3-1.7b</t>
+        </is>
+      </c>
+      <c r="B8" s="17" t="inlineStr">
+        <is>
+          <t>pfw-tail</t>
+        </is>
+      </c>
+      <c r="C8" s="17" t="inlineStr">
+        <is>
+          <t>dpo</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>54</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>47</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>59</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>160</v>
+      </c>
+      <c r="I8" s="14" t="n">
+        <v>0.5219</v>
+      </c>
+      <c r="J8" s="18" t="n">
+        <v>0.5125</v>
+      </c>
+      <c r="K8" s="18" t="n">
+        <v>0.5312</v>
+      </c>
+      <c r="L8" s="6" t="n">
+        <v>966858</v>
+      </c>
+      <c r="M8" s="6" t="n">
+        <v>16012</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="17" t="inlineStr">
+        <is>
+          <t>qwen3-1.7b</t>
+        </is>
+      </c>
+      <c r="B9" s="17" t="inlineStr">
+        <is>
+          <t>pfw-tail</t>
+        </is>
+      </c>
+      <c r="C9" s="17" t="inlineStr">
+        <is>
+          <t>wpo</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>46</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>35</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>79</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>160</v>
+      </c>
+      <c r="I9" s="14" t="n">
+        <v>0.5344</v>
+      </c>
+      <c r="J9" s="18" t="n">
+        <v>0.5312</v>
+      </c>
+      <c r="K9" s="18" t="n">
+        <v>0.5375</v>
+      </c>
+      <c r="L9" s="6" t="n">
+        <v>988544</v>
+      </c>
+      <c r="M9" s="6" t="n">
+        <v>15382</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="17" t="inlineStr">
+        <is>
+          <t>qwen3-1.7b</t>
+        </is>
+      </c>
+      <c r="B10" s="17" t="inlineStr">
+        <is>
+          <t>pfw-tail</t>
+        </is>
+      </c>
+      <c r="C10" s="17" t="inlineStr">
+        <is>
+          <t>radpo</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>77</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>22</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>61</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>160</v>
+      </c>
+      <c r="I10" s="15" t="n">
+        <v>0.6719000000000001</v>
+      </c>
+      <c r="J10" s="18" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="K10" s="18" t="n">
+        <v>0.6438</v>
+      </c>
+      <c r="L10" s="6" t="n">
+        <v>989128</v>
+      </c>
+      <c r="M10" s="6" t="n">
+        <v>15119</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="17" t="inlineStr">
+        <is>
+          <t>qwen3-1.7b</t>
+        </is>
+      </c>
+      <c r="B11" s="17" t="inlineStr">
+        <is>
+          <t>pfw-tail</t>
+        </is>
+      </c>
+      <c r="C11" s="17" t="inlineStr">
+        <is>
+          <t>dckd</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>56</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>79</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>160</v>
+      </c>
+      <c r="I11" s="16" t="n">
+        <v>0.4031</v>
+      </c>
+      <c r="J11" s="18" t="n">
+        <v>0.4062</v>
+      </c>
+      <c r="K11" s="18" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L11" s="6" t="n">
+        <v>704426</v>
+      </c>
+      <c r="M11" s="6" t="n">
+        <v>22940</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="17" t="inlineStr">
+        <is>
+          <t>qwen3-1.7b</t>
+        </is>
+      </c>
+      <c r="B12" s="17" t="inlineStr">
+        <is>
+          <t>pfw-tail</t>
+        </is>
+      </c>
+      <c r="C12" s="17" t="inlineStr">
+        <is>
+          <t>adpa</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>122</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>37</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>160</v>
+      </c>
+      <c r="I12" s="15" t="n">
+        <v>0.8781</v>
+      </c>
+      <c r="J12" s="18" t="n">
+        <v>0.8938</v>
+      </c>
+      <c r="K12" s="18" t="n">
+        <v>0.8625</v>
+      </c>
+      <c r="L12" s="6" t="n">
+        <v>870126</v>
+      </c>
+      <c r="M12" s="6" t="n">
+        <v>20874</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="17" t="inlineStr">
+        <is>
+          <t>qwen3-1.7b</t>
+        </is>
+      </c>
+      <c r="B13" s="17" t="inlineStr">
+        <is>
+          <t>pfw-tail</t>
+        </is>
+      </c>
+      <c r="C13" s="17" t="inlineStr">
+        <is>
+          <t>tvkd</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>59</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>24</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>77</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>160</v>
+      </c>
+      <c r="I13" s="15" t="n">
+        <v>0.6094000000000001</v>
+      </c>
+      <c r="J13" s="18" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K13" s="18" t="n">
+        <v>0.6188</v>
+      </c>
+      <c r="L13" s="6" t="n">
+        <v>985472</v>
+      </c>
+      <c r="M13" s="6" t="n">
+        <v>16026</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="17" t="inlineStr">
+        <is>
+          <t>qwen3-1.7b</t>
+        </is>
+      </c>
+      <c r="B14" s="17" t="inlineStr">
+        <is>
+          <t>riskKD</t>
+        </is>
+      </c>
+      <c r="C14" s="17" t="inlineStr">
+        <is>
+          <t>dpo</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>42</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>48</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>68</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>158</v>
+      </c>
+      <c r="I14" s="14" t="n">
+        <v>0.481</v>
+      </c>
+      <c r="J14" s="18" t="n">
+        <v>0.5437</v>
+      </c>
+      <c r="K14" s="18" t="n">
+        <v>0.4167</v>
+      </c>
+      <c r="L14" s="6" t="n">
+        <v>960664</v>
+      </c>
+      <c r="M14" s="6" t="n">
+        <v>15428</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="17" t="inlineStr">
+        <is>
+          <t>qwen3-1.7b</t>
+        </is>
+      </c>
+      <c r="B15" s="17" t="inlineStr">
+        <is>
+          <t>riskKD</t>
+        </is>
+      </c>
+      <c r="C15" s="17" t="inlineStr">
+        <is>
+          <t>wpo</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>46</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>42</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>72</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>160</v>
+      </c>
+      <c r="I15" s="14" t="n">
+        <v>0.5125</v>
+      </c>
+      <c r="J15" s="18" t="n">
+        <v>0.5437</v>
+      </c>
+      <c r="K15" s="18" t="n">
+        <v>0.4813</v>
+      </c>
+      <c r="L15" s="6" t="n">
+        <v>982350</v>
+      </c>
+      <c r="M15" s="6" t="n">
+        <v>15411</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="17" t="inlineStr">
+        <is>
+          <t>qwen3-1.7b</t>
+        </is>
+      </c>
+      <c r="B16" s="17" t="inlineStr">
+        <is>
+          <t>riskKD</t>
+        </is>
+      </c>
+      <c r="C16" s="17" t="inlineStr">
+        <is>
+          <t>radpo</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>74</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>26</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>160</v>
+      </c>
+      <c r="I16" s="15" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="J16" s="18" t="n">
+        <v>0.675</v>
+      </c>
+      <c r="K16" s="18" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="L16" s="6" t="n">
+        <v>982934</v>
+      </c>
+      <c r="M16" s="6" t="n">
+        <v>16110</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="17" t="inlineStr">
+        <is>
+          <t>qwen3-1.7b</t>
+        </is>
+      </c>
+      <c r="B17" s="17" t="inlineStr">
+        <is>
+          <t>riskKD</t>
+        </is>
+      </c>
+      <c r="C17" s="17" t="inlineStr">
+        <is>
+          <t>dckd</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>27</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>59</v>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>74</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>160</v>
+      </c>
+      <c r="I17" s="16" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J17" s="18" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="K17" s="18" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="L17" s="6" t="n">
+        <v>698232</v>
+      </c>
+      <c r="M17" s="6" t="n">
+        <v>21556</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="17" t="inlineStr">
+        <is>
+          <t>qwen3-1.7b</t>
+        </is>
+      </c>
+      <c r="B18" s="17" t="inlineStr">
+        <is>
+          <t>riskKD</t>
+        </is>
+      </c>
+      <c r="C18" s="17" t="inlineStr">
+        <is>
+          <t>adpa</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>127</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>160</v>
+      </c>
+      <c r="I18" s="15" t="n">
+        <v>0.8875</v>
+      </c>
+      <c r="J18" s="18" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="K18" s="18" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="L18" s="6" t="n">
+        <v>863932</v>
+      </c>
+      <c r="M18" s="6" t="n">
+        <v>19674</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="17" t="inlineStr">
+        <is>
+          <t>qwen3-1.7b</t>
+        </is>
+      </c>
+      <c r="B19" s="17" t="inlineStr">
+        <is>
+          <t>riskKD</t>
+        </is>
+      </c>
+      <c r="C19" s="17" t="inlineStr">
+        <is>
+          <t>tvkd</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>70</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>29</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>61</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>160</v>
+      </c>
+      <c r="I19" s="15" t="n">
+        <v>0.6281</v>
+      </c>
+      <c r="J19" s="18" t="n">
+        <v>0.6562</v>
+      </c>
+      <c r="K19" s="18" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L19" s="6" t="n">
+        <v>979278</v>
+      </c>
+      <c r="M19" s="6" t="n">
+        <v>15283</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="17" t="inlineStr">
+        <is>
+          <t>llama-3.2-1b</t>
+        </is>
+      </c>
+      <c r="B20" s="17" t="inlineStr">
+        <is>
+          <t>tailriskKD</t>
+        </is>
+      </c>
+      <c r="C20" s="17" t="inlineStr">
+        <is>
+          <t>dckd</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>22</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>48</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>160</v>
+      </c>
+      <c r="I20" s="16" t="n">
+        <v>0.2875</v>
+      </c>
+      <c r="J20" s="18" t="n">
+        <v>0.2938</v>
+      </c>
+      <c r="K20" s="18" t="n">
+        <v>0.2812</v>
+      </c>
+      <c r="L20" s="6" t="n">
+        <v>785568</v>
+      </c>
+      <c r="M20" s="6" t="n">
+        <v>27506</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="17" t="inlineStr">
+        <is>
+          <t>llama-3.2-1b</t>
+        </is>
+      </c>
+      <c r="B21" s="17" t="inlineStr">
+        <is>
+          <t>tailriskKD</t>
+        </is>
+      </c>
+      <c r="C21" s="17" t="inlineStr">
+        <is>
+          <t>adpa</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>136</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>24</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>160</v>
+      </c>
+      <c r="I21" s="15" t="n">
+        <v>0.925</v>
+      </c>
+      <c r="J21" s="18" t="n">
+        <v>0.925</v>
+      </c>
+      <c r="K21" s="18" t="n">
+        <v>0.925</v>
+      </c>
+      <c r="L21" s="6" t="n">
+        <v>1058030</v>
+      </c>
+      <c r="M21" s="6" t="n">
+        <v>23620</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="17" t="inlineStr">
+        <is>
+          <t>llama-3.2-1b</t>
+        </is>
+      </c>
+      <c r="B22" s="17" t="inlineStr">
+        <is>
+          <t>tailriskKD</t>
+        </is>
+      </c>
+      <c r="C22" s="17" t="inlineStr">
+        <is>
+          <t>tvkd</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>49</v>
+      </c>
+      <c r="F22" s="6" t="n">
+        <v>65</v>
+      </c>
+      <c r="G22" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>159</v>
+      </c>
+      <c r="I22" s="14" t="n">
+        <v>0.4874</v>
+      </c>
+      <c r="J22" s="18" t="n">
+        <v>0.4938</v>
+      </c>
+      <c r="K22" s="18" t="n">
+        <v>0.481</v>
+      </c>
+      <c r="L22" s="6" t="n">
+        <v>1056636</v>
+      </c>
+      <c r="M22" s="6" t="n">
+        <v>22951</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="17" t="inlineStr">
+        <is>
+          <t>llama-3.2-1b</t>
+        </is>
+      </c>
+      <c r="B23" s="17" t="inlineStr">
+        <is>
+          <t>pfw-tail</t>
+        </is>
+      </c>
+      <c r="C23" s="17" t="inlineStr">
+        <is>
+          <t>dckd</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>24</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>107</v>
+      </c>
+      <c r="F23" s="6" t="n">
+        <v>29</v>
+      </c>
+      <c r="G23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="6" t="n">
+        <v>160</v>
+      </c>
+      <c r="I23" s="16" t="n">
+        <v>0.2406</v>
+      </c>
+      <c r="J23" s="18" t="n">
+        <v>0.2313</v>
+      </c>
+      <c r="K23" s="18" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L23" s="6" t="n">
+        <v>792212</v>
+      </c>
+      <c r="M23" s="6" t="n">
+        <v>26734</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="17" t="inlineStr">
+        <is>
+          <t>llama-3.2-1b</t>
+        </is>
+      </c>
+      <c r="B24" s="17" t="inlineStr">
+        <is>
+          <t>pfw-tail</t>
+        </is>
+      </c>
+      <c r="C24" s="17" t="inlineStr">
+        <is>
+          <t>adpa</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="n">
+        <v>134</v>
+      </c>
+      <c r="E24" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>160</v>
+      </c>
+      <c r="I24" s="15" t="n">
+        <v>0.9156</v>
+      </c>
+      <c r="J24" s="18" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="K24" s="18" t="n">
+        <v>0.9313</v>
+      </c>
+      <c r="L24" s="6" t="n">
+        <v>1064674</v>
+      </c>
+      <c r="M24" s="6" t="n">
+        <v>23553</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="17" t="inlineStr">
+        <is>
+          <t>llama-3.2-1b</t>
+        </is>
+      </c>
+      <c r="B25" s="17" t="inlineStr">
+        <is>
+          <t>pfw-tail</t>
+        </is>
+      </c>
+      <c r="C25" s="17" t="inlineStr">
+        <is>
+          <t>tvkd</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>48</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>61</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>51</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>160</v>
+      </c>
+      <c r="I25" s="14" t="n">
+        <v>0.4594</v>
+      </c>
+      <c r="J25" s="18" t="n">
+        <v>0.475</v>
+      </c>
+      <c r="K25" s="18" t="n">
+        <v>0.4437</v>
+      </c>
+      <c r="L25" s="6" t="n">
+        <v>1063280</v>
+      </c>
+      <c r="M25" s="6" t="n">
+        <v>23447</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="17" t="inlineStr">
+        <is>
+          <t>llama-3.2-1b</t>
+        </is>
+      </c>
+      <c r="B26" s="17" t="inlineStr">
+        <is>
+          <t>riskkd (tokenwt)</t>
+        </is>
+      </c>
+      <c r="C26" s="17" t="inlineStr">
+        <is>
+          <t>dckd</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="E26" s="6" t="n">
+        <v>141</v>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="G26" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="6" t="n">
+        <v>160</v>
+      </c>
+      <c r="I26" s="16" t="n">
+        <v>0.07190000000000001</v>
+      </c>
+      <c r="J26" s="18" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="K26" s="18" t="n">
+        <v>0.0813</v>
+      </c>
+      <c r="L26" s="6" t="n">
+        <v>797652</v>
+      </c>
+      <c r="M26" s="6" t="n">
+        <v>27860</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="17" t="inlineStr">
+        <is>
+          <t>llama-3.2-1b</t>
+        </is>
+      </c>
+      <c r="B27" s="17" t="inlineStr">
+        <is>
+          <t>riskkd (tokenwt)</t>
+        </is>
+      </c>
+      <c r="C27" s="17" t="inlineStr">
+        <is>
+          <t>adpa</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="n">
+        <v>77</v>
+      </c>
+      <c r="E27" s="6" t="n">
+        <v>24</v>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>59</v>
+      </c>
+      <c r="G27" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="6" t="n">
+        <v>160</v>
+      </c>
+      <c r="I27" s="15" t="n">
+        <v>0.6656</v>
+      </c>
+      <c r="J27" s="18" t="n">
+        <v>0.6125</v>
+      </c>
+      <c r="K27" s="18" t="n">
+        <v>0.7188</v>
+      </c>
+      <c r="L27" s="6" t="n">
+        <v>1070114</v>
+      </c>
+      <c r="M27" s="6" t="n">
+        <v>25637</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="17" t="inlineStr">
+        <is>
+          <t>llama-3.2-1b</t>
+        </is>
+      </c>
+      <c r="B28" s="17" t="inlineStr">
+        <is>
+          <t>riskkd (tokenwt)</t>
+        </is>
+      </c>
+      <c r="C28" s="17" t="inlineStr">
+        <is>
+          <t>tvkd</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E28" s="6" t="n">
+        <v>135</v>
+      </c>
+      <c r="F28" s="6" t="n">
+        <v>22</v>
+      </c>
+      <c r="G28" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="6" t="n">
+        <v>160</v>
+      </c>
+      <c r="I28" s="16" t="n">
+        <v>0.08749999999999999</v>
+      </c>
+      <c r="J28" s="18" t="n">
+        <v>0.09379999999999999</v>
+      </c>
+      <c r="K28" s="18" t="n">
+        <v>0.0813</v>
+      </c>
+      <c r="L28" s="6" t="n">
+        <v>1068720</v>
+      </c>
+      <c r="M28" s="6" t="n">
+        <v>22748</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>